--- a/dataset/01.w_Defects/free_null_pointer.xlsx
+++ b/dataset/01.w_Defects/free_null_pointer.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#define ZERO 0 #define ZERO 0 int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; define ZERO 0 void free_null_pointer_007() { int flag=0,i,j; free_null_pointer_007_gbl_doubleptr=NULL; goto label; if(free_null_pointer_007_func_001(flag)!=ZERO) { for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { free_null_pointer_007_gbl_doubleptr[i][j] += 1; } free (free_null_pointer_007_gbl_doubleptr[i]); free_null_pointer_007_gbl_doubleptr[i] = NULL; } } else { free(free_null_pointer_007_gbl_doubleptr);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ free_null_pointer_007_gbl_doubleptr = NULL; } label: if(free_null_pointer_007_func_001(flag)!=ZERO) { free_null_pointer_007_func_002(); } } void free_null_pointer_007_func_002() { int i,j; free_null_pointer_007_gbl_doubleptr=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { free_null_pointer_007_gbl_doubleptr[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { free_null_pointer_007_gbl_doubleptr[i][j]=i; } } } int free_null_pointer_007_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>#define ZERO 0 #define ZERO 0 int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; define ZERO 0 void free_null_pointer_007() { int flag=0,i,j; free_null_pointer_007_gbl_doubleptr=NULL; goto label; if(free_null_pointer_007_func_001(flag)!=ZERO) { for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { free_null_pointer_007_gbl_doubleptr[i][j] += 1; } free (free_null_pointer_007_gbl_doubleptr[i]); free_null_pointer_007_gbl_doubleptr[i] = NULL; } } else { free(free_null_pointer_007_gbl_doubleptr);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ free_null_pointer_007_gbl_doubleptr = NULL; } label: if(free_null_pointer_007_func_001(flag)!=ZERO) { free_null_pointer_007_func_002(); } } int free_null_pointer_007_func_001(int flag) { int ret ; if (flag ==0) ret = 0; else ret=1; return ret; } void free_null_pointer_007_func_002() { int i,j; free_null_pointer_007_gbl_doubleptr=(long**) malloc(10*sizeof(long*)); for(i=0;i&lt;10;i++) { free_null_pointer_007_gbl_doubleptr[i]=(long*) malloc(10*sizeof(long)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { free_null_pointer_007_gbl_doubleptr[i][j]=i; } } }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>typedef union { int a; int b; } free_null_pointer_011_u_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_011 () { int ret; free_null_pointer_011_u_001 *p; p = free_null_pointer_011_func_001 (); ret = p-&gt;b; p = free_null_pointer_011_func_002 (); } free_null_pointer_011_u_001 * free_null_pointer_011_func_001 () { int flag = 0; switch (flag) { case 1: { u = (free_null_pointer_011_u_001 *)calloc(1,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 40; return u; } case 2: { u = (free_null_pointer_011_u_001 *)calloc(2,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 20; return u; } case 3: { u = (free_null_pointer_011_u_001 *)calloc(3,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 30; return u; } default: return (free_null_pointer_011_u_001 *)(-1); } } free_null_pointer_011_u_001 * free_null_pointer_011_func_002 () { int flag = rand(); switch (flag) { case 1: { free(u); /* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ u= NULL; return u; } case 2: { return u; } case 3: { return u; } default: return (free_null_pointer_011_u_001 *)(-1); } }</t>
+          <t>typedef union { int a; int b; } free_null_pointer_011_u_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_011 () { int ret; free_null_pointer_011_u_001 *p; p = free_null_pointer_011_func_001 (); ret = p-&gt;b; p = free_null_pointer_011_func_002 (); } free_null_pointer_011_u_001 * free_null_pointer_011_func_002 () { int flag = rand(); switch (flag) { case 1: { free(u); /* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ u= NULL; return u; } case 2: { return u; } case 3: { return u; } default: return (free_null_pointer_011_u_001 *)(-1); } } free_null_pointer_011_u_001 * free_null_pointer_011_func_001 () { int flag = 0; switch (flag) { case 1: { u = (free_null_pointer_011_u_001 *)calloc(1,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 40; return u; } case 2: { u = (free_null_pointer_011_u_001 *)calloc(2,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 20; return u; } case 3: { u = (free_null_pointer_011_u_001 *)calloc(3,sizeof(free_null_pointer_011_u_001)); u-&gt;a = 30; return u; } default: return (free_null_pointer_011_u_001 *)(-1); } }</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>typedef struct { double *p1; double *p2; double *p3; } free_null_pointer_014_s_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_014 () { free_null_pointer_014_func_001(1); free_null_pointer_014_func_002(1); free_null_pointer_014_func_003(1); } void free_null_pointer_014_func_002(int flag) { static double arr[3]={10.0,20.0,30.0}; int i; if (flag ==1) { for (i=0;i&lt;1;i++) { *(free_null_pointer_014_gbl_s-&gt;p1) = arr[0]; *(free_null_pointer_014_gbl_s-&gt;p2) = arr[1]; *(free_null_pointer_014_gbl_s-&gt;p3) = arr[2]; } } } void free_null_pointer_014_func_001(int flag) { int i; if(flag ==1) { for (i=1;i&lt;1;i++) { free_null_pointer_014_gbl_s = malloc(sizeof(free_null_pointer_014_s_001)); free_null_pointer_014_gbl_s-&gt;p1 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p2 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p3 = malloc(sizeof(double)); } } } void free_null_pointer_014_func_003(int flag) { int i; if (flag ==1) { for (i=1;i&lt;1;i++) { free(free_null_pointer_014_gbl_s-&gt;p1); free(free_null_pointer_014_gbl_s-&gt;p2); free(free_null_pointer_014_gbl_s-&gt;p3); } for (i=0;i&lt;1;i++) { free(free_null_pointer_014_gbl_s);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ } } }</t>
+          <t>typedef struct { double *p1; double *p2; double *p3; } free_null_pointer_014_s_001; int *free_null_pointer_002_gbl_ptr = NULL; char **free_null_pointer_010_gbl_dst=NULL; static unsigned char a =INDEX; char * free_null_pointer_005_gbl_ptr; long ** free_null_pointer_007_gbl_doubleptr; enum {min_buffer = 0 , max_buffer = 5 }; static unsigned int min=min_buffer+2; static unsigned int max=max_buffer+2; char **free_null_pointer_009dst; static free_null_pointer_011_u_001 *u; free_null_pointer_014_s_001 *free_null_pointer_014_gbl_s=NULL; extern volatile int vflag; void free_null_pointer_014 () { free_null_pointer_014_func_001(1); free_null_pointer_014_func_002(1); free_null_pointer_014_func_003(1); } void free_null_pointer_014_func_002(int flag) { static double arr[3]={10.0,20.0,30.0}; int i; if (flag ==1) { for (i=0;i&lt;1;i++) { *(free_null_pointer_014_gbl_s-&gt;p1) = arr[0]; *(free_null_pointer_014_gbl_s-&gt;p2) = arr[1]; *(free_null_pointer_014_gbl_s-&gt;p3) = arr[2]; } } } void free_null_pointer_014_func_003(int flag) { int i; if (flag ==1) { for (i=1;i&lt;1;i++) { free(free_null_pointer_014_gbl_s-&gt;p1); free(free_null_pointer_014_gbl_s-&gt;p2); free(free_null_pointer_014_gbl_s-&gt;p3); } for (i=0;i&lt;1;i++) { free(free_null_pointer_014_gbl_s);/* Tool should detect this line as error *//*ERROR:Freeing a NULL pointer*/ } } } void free_null_pointer_014_func_001(int flag) { int i; if(flag ==1) { for (i=1;i&lt;1;i++) { free_null_pointer_014_gbl_s = malloc(sizeof(free_null_pointer_014_s_001)); free_null_pointer_014_gbl_s-&gt;p1 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p2 = malloc(sizeof(double)); free_null_pointer_014_gbl_s-&gt;p3 = malloc(sizeof(double)); } } }</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
